--- a/Excel/Labs/lab1-solution.xlsx
+++ b/Excel/Labs/lab1-solution.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\core2duo\Desktop\Excel\Labs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\core2duo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C360A1CA-51BA-4DAD-BDB5-43BF1E9FD60B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C6AD48-7360-4A13-BC3D-5B0CEE8A6D1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6E0772BF-1D0C-417B-A4B2-B12690A11A9F}"/>
+    <workbookView xWindow="4020" yWindow="2412" windowWidth="14520" windowHeight="8880" xr2:uid="{6E0772BF-1D0C-417B-A4B2-B12690A11A9F}"/>
   </bookViews>
   <sheets>
     <sheet name="EX1" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="64">
   <si>
     <t>#</t>
   </si>
@@ -91,9 +91,6 @@
   </si>
   <si>
     <t>Emp_ID</t>
-  </si>
-  <si>
-    <t>Emp_Name</t>
   </si>
   <si>
     <t>Ahmed</t>
@@ -239,6 +236,12 @@
   <si>
     <t>Gov</t>
   </si>
+  <si>
+    <t>INDEX MATCH</t>
+  </si>
+  <si>
+    <t>Emp_Name (Vlookup)</t>
+  </si>
 </sst>
 </file>
 
@@ -248,8 +251,8 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="#,##0.00000"/>
-    <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="170" formatCode="[$EGP]\ #,##0.00_);\([$EGP]\ #,##0.00\)"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="[$EGP]\ #,##0.00_);\([$EGP]\ #,##0.00\)"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -736,6 +739,18 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -751,18 +766,6 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="1" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="5" builtinId="3"/>
@@ -772,7 +775,7 @@
     <cellStyle name="Normal 2" xfId="1" xr:uid="{38AF7B54-7C91-4C1A-A730-67FD4A2324F8}"/>
     <cellStyle name="عادي 2" xfId="3" xr:uid="{558F22E9-9660-430D-A588-08C9DFFD9DBD}"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -790,16 +793,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -12797,15 +12790,15 @@
   <sheetPr>
     <tabColor theme="3" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:P36"/>
+  <dimension ref="A1:Q36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="3" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.6640625" style="20" customWidth="1"/>
     <col min="3" max="3" width="22.44140625" style="20" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.6640625" style="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5546875" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.33203125" style="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.77734375" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.77734375" style="19" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.109375" style="4" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.109375" style="13" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.44140625" style="13" bestFit="1" customWidth="1"/>
@@ -12815,11 +12808,12 @@
     <col min="13" max="13" width="10.33203125" style="13" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="2.33203125" style="13" customWidth="1"/>
     <col min="15" max="15" width="8.44140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.5546875" style="4" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="4"/>
+    <col min="16" max="16" width="19.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.44140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -12864,18 +12858,21 @@
         <v>13</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>14</v>
+        <v>63</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:17">
       <c r="A2" s="5">
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>15</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>16</v>
       </c>
       <c r="D2" s="7">
         <v>671.49631999999997</v>
@@ -12883,11 +12880,11 @@
       <c r="E2" s="5">
         <v>31</v>
       </c>
-      <c r="F2" s="51">
+      <c r="F2" s="46">
         <f>D2*$E$2</f>
         <v>20816.385920000001</v>
       </c>
-      <c r="G2" s="50">
+      <c r="G2" s="45">
         <f>ROUND(F2,0)</f>
         <v>20816</v>
       </c>
@@ -12904,8 +12901,8 @@
         <v>Ahmed Yassin</v>
       </c>
       <c r="K2" s="5">
-        <f>LEN(J2)</f>
-        <v>12</v>
+        <f>LEN(SUBSTITUTE(J2," ",""))</f>
+        <v>11</v>
       </c>
       <c r="L2" s="9" t="str">
         <f>LEFT(J2,1)</f>
@@ -12923,16 +12920,20 @@
         <f>VLOOKUP(O2,'Vlookup sheet'!$A$1:$B$15,2,TRUE)</f>
         <v>Mazen Sameh</v>
       </c>
+      <c r="Q2" s="12" t="str">
+        <f>INDEX('Vlookup sheet'!B2:B15, MATCH('EX1'!O2, 'Vlookup sheet'!A2:A15, 0))</f>
+        <v>Mazen Sameh</v>
+      </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:17">
       <c r="A3" s="5">
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>17</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>18</v>
       </c>
       <c r="D3" s="7">
         <v>830</v>
@@ -12940,11 +12941,11 @@
       <c r="E3" s="5">
         <v>40</v>
       </c>
-      <c r="F3" s="51">
+      <c r="F3" s="46">
         <f t="shared" ref="F3:F11" si="0">D3*$E$2</f>
         <v>25730</v>
       </c>
-      <c r="G3" s="50">
+      <c r="G3" s="45">
         <f t="shared" ref="G3:G11" si="1">ROUND(F3,0)</f>
         <v>25730</v>
       </c>
@@ -12961,8 +12962,8 @@
         <v>Mohamed ismail</v>
       </c>
       <c r="K3" s="5">
-        <f t="shared" ref="K3:K11" si="5">LEN(J3)</f>
-        <v>14</v>
+        <f t="shared" ref="K3:K11" si="5">LEN(SUBSTITUTE(J3," ",""))</f>
+        <v>13</v>
       </c>
       <c r="L3" s="9" t="str">
         <f t="shared" ref="L3:L11" si="6">LEFT(J3,1)</f>
@@ -12980,16 +12981,17 @@
         <f>VLOOKUP(O3,'Vlookup sheet'!$A$1:$B$15,2,TRUE)</f>
         <v>eamy hassan</v>
       </c>
+      <c r="Q3" s="12"/>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:17">
       <c r="A4" s="5">
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>20</v>
       </c>
       <c r="D4" s="7">
         <v>886.20654000000002</v>
@@ -12997,11 +12999,11 @@
       <c r="E4" s="5">
         <v>41</v>
       </c>
-      <c r="F4" s="51">
+      <c r="F4" s="46">
         <f t="shared" si="0"/>
         <v>27472.402740000001</v>
       </c>
-      <c r="G4" s="50">
+      <c r="G4" s="45">
         <f t="shared" si="1"/>
         <v>27472</v>
       </c>
@@ -13019,7 +13021,7 @@
       </c>
       <c r="K4" s="5">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L4" s="9" t="str">
         <f t="shared" si="6"/>
@@ -13037,16 +13039,17 @@
         <f>VLOOKUP(O4,'Vlookup sheet'!$A$1:$B$15,2,TRUE)</f>
         <v>maha ahmed</v>
       </c>
+      <c r="Q4" s="12"/>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:17">
       <c r="A5" s="5">
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>21</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>22</v>
       </c>
       <c r="D5" s="7">
         <v>950.28737000000001</v>
@@ -13054,11 +13057,11 @@
       <c r="E5" s="5">
         <v>42</v>
       </c>
-      <c r="F5" s="51">
+      <c r="F5" s="46">
         <f t="shared" si="0"/>
         <v>29458.908470000002</v>
       </c>
-      <c r="G5" s="50">
+      <c r="G5" s="45">
         <f t="shared" si="1"/>
         <v>29459</v>
       </c>
@@ -13076,7 +13079,7 @@
       </c>
       <c r="K5" s="5">
         <f t="shared" si="5"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L5" s="9" t="str">
         <f t="shared" si="6"/>
@@ -13094,16 +13097,17 @@
         <f>VLOOKUP(O5,'Vlookup sheet'!$A$1:$B$15,2,TRUE)</f>
         <v>mohamed ismail</v>
       </c>
+      <c r="Q5" s="12"/>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:17">
       <c r="A6" s="5">
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D6" s="7">
         <v>558.93357000000003</v>
@@ -13111,11 +13115,11 @@
       <c r="E6" s="5">
         <v>30.89</v>
       </c>
-      <c r="F6" s="51">
+      <c r="F6" s="46">
         <f t="shared" si="0"/>
         <v>17326.94067</v>
       </c>
-      <c r="G6" s="50">
+      <c r="G6" s="45">
         <f t="shared" si="1"/>
         <v>17327</v>
       </c>
@@ -13133,7 +13137,7 @@
       </c>
       <c r="K6" s="5">
         <f t="shared" si="5"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L6" s="9" t="str">
         <f t="shared" si="6"/>
@@ -13151,16 +13155,17 @@
         <f>VLOOKUP(O6,'Vlookup sheet'!$A$1:$B$15,2,TRUE)</f>
         <v>ahmed fawzy</v>
       </c>
+      <c r="Q6" s="12"/>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:17">
       <c r="A7" s="5">
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>24</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>25</v>
       </c>
       <c r="D7" s="7">
         <v>500</v>
@@ -13168,11 +13173,11 @@
       <c r="E7" s="5">
         <v>49</v>
       </c>
-      <c r="F7" s="51">
+      <c r="F7" s="46">
         <f t="shared" si="0"/>
         <v>15500</v>
       </c>
-      <c r="G7" s="50">
+      <c r="G7" s="45">
         <f t="shared" si="1"/>
         <v>15500</v>
       </c>
@@ -13190,7 +13195,7 @@
       </c>
       <c r="K7" s="5">
         <f t="shared" si="5"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L7" s="9" t="str">
         <f t="shared" si="6"/>
@@ -13208,16 +13213,17 @@
         <f>VLOOKUP(O7,'Vlookup sheet'!$A$1:$B$15,2,TRUE)</f>
         <v>kamal Hussien</v>
       </c>
+      <c r="Q7" s="12"/>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:17">
       <c r="A8" s="5">
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D8" s="7">
         <v>825.70673999999997</v>
@@ -13225,11 +13231,11 @@
       <c r="E8" s="5">
         <v>47</v>
       </c>
-      <c r="F8" s="51">
+      <c r="F8" s="46">
         <f t="shared" si="0"/>
         <v>25596.908939999998</v>
       </c>
-      <c r="G8" s="50">
+      <c r="G8" s="45">
         <f t="shared" si="1"/>
         <v>25597</v>
       </c>
@@ -13247,7 +13253,7 @@
       </c>
       <c r="K8" s="5">
         <f t="shared" si="5"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L8" s="9" t="str">
         <f t="shared" si="6"/>
@@ -13265,16 +13271,17 @@
         <f>VLOOKUP(O8,'Vlookup sheet'!$A$1:$B$15,2,TRUE)</f>
         <v>eyad ahmed</v>
       </c>
+      <c r="Q8" s="12"/>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:17">
       <c r="A9" s="5">
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>27</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>28</v>
       </c>
       <c r="D9" s="7">
         <v>931.85544000000004</v>
@@ -13282,11 +13289,11 @@
       <c r="E9" s="5">
         <v>30.89</v>
       </c>
-      <c r="F9" s="51">
+      <c r="F9" s="46">
         <f t="shared" si="0"/>
         <v>28887.518640000002</v>
       </c>
-      <c r="G9" s="50">
+      <c r="G9" s="45">
         <f t="shared" si="1"/>
         <v>28888</v>
       </c>
@@ -13304,7 +13311,7 @@
       </c>
       <c r="K9" s="5">
         <f t="shared" si="5"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L9" s="9" t="str">
         <f t="shared" si="6"/>
@@ -13322,16 +13329,17 @@
         <f>VLOOKUP(O9,'Vlookup sheet'!$A$1:$B$15,2,TRUE)</f>
         <v>yamen mohamed</v>
       </c>
+      <c r="Q9" s="12"/>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:17">
       <c r="A10" s="5">
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>29</v>
       </c>
       <c r="D10" s="7">
         <v>567.52768000000003</v>
@@ -13339,11 +13347,11 @@
       <c r="E10" s="5">
         <v>30.89</v>
       </c>
-      <c r="F10" s="51">
+      <c r="F10" s="46">
         <f t="shared" si="0"/>
         <v>17593.358080000002</v>
       </c>
-      <c r="G10" s="50">
+      <c r="G10" s="45">
         <f t="shared" si="1"/>
         <v>17593</v>
       </c>
@@ -13361,7 +13369,7 @@
       </c>
       <c r="K10" s="5">
         <f t="shared" si="5"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L10" s="9" t="str">
         <f t="shared" si="6"/>
@@ -13379,16 +13387,17 @@
         <f>VLOOKUP(O10,'Vlookup sheet'!$A$1:$B$15,2,TRUE)</f>
         <v>Mazen Sameh</v>
       </c>
+      <c r="Q10" s="12"/>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:17">
       <c r="A11" s="5">
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D11" s="7">
         <v>957.68445999999994</v>
@@ -13396,11 +13405,11 @@
       <c r="E11" s="5">
         <v>30.89</v>
       </c>
-      <c r="F11" s="51">
+      <c r="F11" s="46">
         <f t="shared" si="0"/>
         <v>29688.218259999998</v>
       </c>
-      <c r="G11" s="50">
+      <c r="G11" s="45">
         <f t="shared" si="1"/>
         <v>29688</v>
       </c>
@@ -13418,7 +13427,7 @@
       </c>
       <c r="K11" s="5">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L11" s="9" t="str">
         <f t="shared" si="6"/>
@@ -13436,8 +13445,9 @@
         <f>VLOOKUP(O11,'Vlookup sheet'!$A$1:$B$15,2,TRUE)</f>
         <v>ali ismail</v>
       </c>
+      <c r="Q11" s="12"/>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:17">
       <c r="A12" s="13"/>
       <c r="B12" s="14"/>
       <c r="C12" s="14"/>
@@ -13451,9 +13461,9 @@
       <c r="O12" s="20"/>
       <c r="P12" s="20"/>
     </row>
-    <row r="13" spans="1:16" ht="15" thickBot="1">
+    <row r="13" spans="1:17" ht="15" thickBot="1">
       <c r="C13" s="21" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" s="22"/>
       <c r="E13" s="23">
@@ -13461,9 +13471,9 @@
         <v>238070.64172000001</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="15" thickBot="1">
+    <row r="14" spans="1:17" ht="15" thickBot="1">
       <c r="C14" s="24" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D14" s="25"/>
       <c r="E14" s="26">
@@ -13472,9 +13482,9 @@
       </c>
       <c r="G14" s="27"/>
     </row>
-    <row r="15" spans="1:16" ht="15" thickBot="1">
+    <row r="15" spans="1:17" ht="15" thickBot="1">
       <c r="C15" s="24" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D15" s="25"/>
       <c r="E15" s="26">
@@ -13483,12 +13493,12 @@
       </c>
       <c r="M15" s="28"/>
     </row>
-    <row r="16" spans="1:16" ht="15" thickBot="1">
+    <row r="16" spans="1:17" ht="15" thickBot="1">
       <c r="C16" s="24" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D16" s="25"/>
-      <c r="E16" s="52">
+      <c r="E16" s="47">
         <f>MIN(F2:F11)</f>
         <v>15500</v>
       </c>
@@ -13497,10 +13507,10 @@
     <row r="17" spans="2:7" ht="15" thickBot="1">
       <c r="B17" s="3"/>
       <c r="C17" s="24" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D17" s="25"/>
-      <c r="E17" s="52">
+      <c r="E17" s="47">
         <f>COUNT(F2:F11)</f>
         <v>10</v>
       </c>
@@ -13508,27 +13518,27 @@
     </row>
     <row r="18" spans="2:7" ht="15" thickBot="1">
       <c r="C18" s="24" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D18" s="25"/>
-      <c r="E18" s="52">
+      <c r="E18" s="47">
         <f>COUNTA(J2:J11)</f>
         <v>10</v>
       </c>
     </row>
     <row r="19" spans="2:7" ht="15" thickBot="1">
       <c r="C19" s="24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D19" s="25"/>
-      <c r="E19" s="52">
+      <c r="E19" s="47">
         <f>COUNTBLANK(J2:J11)</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="2:7" ht="15" thickBot="1">
       <c r="C20" s="24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D20" s="25"/>
       <c r="E20" s="26">
@@ -13538,7 +13548,7 @@
     </row>
     <row r="21" spans="2:7" ht="14.25" customHeight="1" thickBot="1">
       <c r="C21" s="30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D21" s="31"/>
       <c r="E21" s="32">
@@ -13548,80 +13558,80 @@
     </row>
     <row r="22" spans="2:7" ht="15" thickBot="1">
       <c r="C22" s="30" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D22" s="31"/>
-      <c r="E22" s="53">
+      <c r="E22" s="48">
         <f>SUMIF(I2:I11,"Well-paid",F2:F11)</f>
         <v>187650.34297</v>
       </c>
     </row>
     <row r="23" spans="2:7">
       <c r="C23" s="30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D23" s="31"/>
-      <c r="E23" s="53">
+      <c r="E23" s="48">
         <f>COUNTIF(I2:I11,"Well-paid")</f>
         <v>7</v>
       </c>
     </row>
     <row r="26" spans="2:7" ht="23.4">
-      <c r="C26" s="48" t="s">
-        <v>57</v>
-      </c>
-      <c r="D26" s="49"/>
-      <c r="E26" s="49"/>
-      <c r="F26" s="49"/>
-      <c r="G26" s="49"/>
+      <c r="C26" s="52" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" s="53"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53"/>
     </row>
     <row r="28" spans="2:7" ht="18">
       <c r="C28" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="D28" s="45"/>
-      <c r="E28" s="46"/>
-      <c r="F28" s="47"/>
+        <v>30</v>
+      </c>
+      <c r="D28" s="49"/>
+      <c r="E28" s="50"/>
+      <c r="F28" s="51"/>
     </row>
     <row r="29" spans="2:7" ht="18">
       <c r="C29" s="44" t="s">
-        <v>62</v>
-      </c>
-      <c r="D29" s="45"/>
-      <c r="E29" s="46"/>
-      <c r="F29" s="47"/>
+        <v>61</v>
+      </c>
+      <c r="D29" s="49"/>
+      <c r="E29" s="50"/>
+      <c r="F29" s="51"/>
     </row>
     <row r="30" spans="2:7" ht="18">
       <c r="C30" s="44" t="s">
-        <v>58</v>
-      </c>
-      <c r="D30" s="45"/>
-      <c r="E30" s="46"/>
-      <c r="F30" s="47"/>
+        <v>57</v>
+      </c>
+      <c r="D30" s="49"/>
+      <c r="E30" s="50"/>
+      <c r="F30" s="51"/>
     </row>
     <row r="31" spans="2:7" ht="18">
       <c r="C31" s="44" t="s">
-        <v>59</v>
-      </c>
-      <c r="D31" s="45"/>
-      <c r="E31" s="46"/>
-      <c r="F31" s="47"/>
+        <v>58</v>
+      </c>
+      <c r="D31" s="49"/>
+      <c r="E31" s="50"/>
+      <c r="F31" s="51"/>
     </row>
     <row r="32" spans="2:7" ht="18">
       <c r="C32" s="44" t="s">
-        <v>60</v>
-      </c>
-      <c r="D32" s="45"/>
-      <c r="E32" s="46"/>
-      <c r="F32" s="47"/>
+        <v>59</v>
+      </c>
+      <c r="D32" s="49"/>
+      <c r="E32" s="50"/>
+      <c r="F32" s="51"/>
     </row>
     <row r="33" spans="3:6" ht="18">
       <c r="C33" s="44" t="s">
-        <v>61</v>
-      </c>
-      <c r="D33" s="45"/>
-      <c r="E33" s="46"/>
-      <c r="F33" s="47"/>
+        <v>60</v>
+      </c>
+      <c r="D33" s="49"/>
+      <c r="E33" s="50"/>
+      <c r="F33" s="51"/>
     </row>
     <row r="36" spans="3:6">
       <c r="F36" s="33"/>
@@ -13640,8 +13650,8 @@
     <mergeCell ref="D30:F30"/>
   </mergeCells>
   <conditionalFormatting sqref="F2:F11">
+    <cfRule type="top10" dxfId="1" priority="1" bottom="1" rank="1"/>
     <cfRule type="top10" dxfId="0" priority="2" rank="1"/>
-    <cfRule type="top10" dxfId="1" priority="1" bottom="1" rank="1"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="C26" r:id="rId1" xr:uid="{9B35966A-EBE3-463F-89A3-32D052E9D6F3}"/>
@@ -13666,7 +13676,7 @@
         <v>13</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -13674,7 +13684,7 @@
         <v>1001</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -13682,7 +13692,7 @@
         <v>1002</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -13690,7 +13700,7 @@
         <v>1003</v>
       </c>
       <c r="B4" s="41" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -13698,7 +13708,7 @@
         <v>1004</v>
       </c>
       <c r="B5" s="39" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -13706,7 +13716,7 @@
         <v>1005</v>
       </c>
       <c r="B6" s="41" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -13714,7 +13724,7 @@
         <v>1006</v>
       </c>
       <c r="B7" s="39" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -13722,7 +13732,7 @@
         <v>1007</v>
       </c>
       <c r="B8" s="41" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -13730,7 +13740,7 @@
         <v>1008</v>
       </c>
       <c r="B9" s="39" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -13738,7 +13748,7 @@
         <v>1009</v>
       </c>
       <c r="B10" s="41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -13746,7 +13756,7 @@
         <v>1010</v>
       </c>
       <c r="B11" s="39" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -13754,7 +13764,7 @@
         <v>1011</v>
       </c>
       <c r="B12" s="41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -13762,7 +13772,7 @@
         <v>1012</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -13770,7 +13780,7 @@
         <v>1013</v>
       </c>
       <c r="B14" s="41" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -13778,7 +13788,7 @@
         <v>1014</v>
       </c>
       <c r="B15" s="43" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
